--- a/artfynd/A 36700-2025 artfynd.xlsx
+++ b/artfynd/A 36700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95975859</v>
+        <v>95975863</v>
       </c>
       <c r="B2" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>400064.8548257827</v>
+        <v>400093</v>
       </c>
       <c r="R2" t="n">
-        <v>6220857.226713037</v>
+        <v>6220757</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ung</t>
+          <t>Ganska riklig på stenblock</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95975851</v>
+        <v>95975848</v>
       </c>
       <c r="B3" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -829,17 +809,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Perstorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399806.4198034441</v>
+        <v>399756</v>
       </c>
       <c r="R3" t="n">
-        <v>6220676.475108995</v>
+        <v>6220727</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,24 +858,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ung</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,32 +891,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95975856</v>
+        <v>122185703</v>
       </c>
       <c r="B4" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -957,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>399890.4078254079</v>
+        <v>399994</v>
       </c>
       <c r="R4" t="n">
-        <v>6220755.918025224</v>
+        <v>6220731</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,27 +956,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ung</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,31 +986,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Ylva Hanell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Ylva Hanell, Peter Frodin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122185714</v>
+        <v>95975851</v>
       </c>
       <c r="B5" t="n">
-        <v>56342</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208255</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,13 +1033,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>399887</v>
+        <v>399806</v>
       </c>
       <c r="R5" t="n">
-        <v>6220717</v>
+        <v>6220676</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,12 +1063,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ung</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,27 +1088,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ylva Hanell</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ylva Hanell, Peter Frodin</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122185704</v>
+        <v>95975856</v>
       </c>
       <c r="B6" t="n">
-        <v>58215</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,13 +1139,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>399991</v>
+        <v>399890</v>
       </c>
       <c r="R6" t="n">
-        <v>6220724</v>
+        <v>6220756</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,22 +1169,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ung</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1194,329 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>95975859</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Perstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>400065</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6220857</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Perstorp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Perstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ung</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122185704</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Perstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>399991</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6220724</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Perstorp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Perstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Ylva Hanell</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Ylva Hanell, Peter Frodin</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122185714</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Perstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>399887</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6220717</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Perstorp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Perstorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ylva Hanell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ylva Hanell, Peter Frodin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36700-2025 artfynd.xlsx
+++ b/artfynd/A 36700-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95975863</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95975848</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122185703</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95975851</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95975856</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95975859</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122185704</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1517,8 +1557,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122185714</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>